--- a/data/sites/manufacturing/Production Operations/preventive-maintenance-schedule-line-2.xlsx
+++ b/data/sites/manufacturing/Production Operations/preventive-maintenance-schedule-line-2.xlsx
@@ -7,7 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Architecture" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Controls" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 KPIs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 RACI Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Procedures" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +38,15 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,6 +157,186 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,19 +628,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Preventive Maintenance Schedule - Line 2</t>
+          <t>Preventive Maintenance Schedule - Line 2 - Section 1: Executive Summary &amp; Scope</t>
         </is>
       </c>
     </row>
@@ -455,54 +651,2261 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Preventive maintenance task list and interval schedule for critical equipment on Line 2, used to plan planned downtime windows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Key Point</t>
+          <t>Preventive maintenance task list and interval schedule for critical equipment on Line 2, used to plan planned downtime windows. Section 1 (Executive Summary &amp; Scope) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Defines the operational charter, scope boundaries, and executive accountability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 1.1: Lubrication checks on the conveyor drive are performed weekly. Secondary control 1.2: Full gearbox inspection is scheduled quarterly during planned downtime.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Lubrication checks on the conveyor drive are performed weekly.</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Control Area</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full gearbox inspection is scheduled quarterly during planned downtime.</t>
+          <t>Production Operations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Missed PM tasks are automatically rolled into the following week's schedule.</t>
+          <t>Preventive Maintenance Sched Gate 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PM compliance rate is reported alongside the monthly OEE review.</t>
+          <t>Preventive Maintenance Sched Gate 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Monitored</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>• Lubrication checks on the conveyor drive are performed weekly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Full gearbox inspection is scheduled quarterly during planned downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Section 1 review cadence is tracked by Grace Liu under Production Operations governance.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Schedule - Line 2 - Section 10: Cross-Functional Dependencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Preventive maintenance task list and interval schedule for critical equipment on Line 2, used to plan planned downtime windows. Section 10 (Cross-Functional Dependencies) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Documents upstream and downstream team dependencies and service-level commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 10.1: Full gearbox inspection is scheduled quarterly during planned downtime. Secondary control 10.2: Missed PM tasks are automatically rolled into the following week's schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Control Area</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Production Operations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Monitored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 10 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Full gearbox inspection is scheduled quarterly during planned downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Missed PM tasks are automatically rolled into the following week's schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 10 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Schedule - Line 2 - Section 11: Continuous Improvement Roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Preventive maintenance task list and interval schedule for critical equipment on Line 2, used to plan planned downtime windows. Section 11 (Continuous Improvement Roadmap) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 11.1: Missed PM tasks are automatically rolled into the following week's schedule. Secondary control 11.2: PM compliance rate is reported alongside the monthly OEE review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Control Area</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Production Operations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Monitored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 11 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Missed PM tasks are automatically rolled into the following week's schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• PM compliance rate is reported alongside the monthly OEE review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 11 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Schedule - Line 2 - Section 12: Appendix, Lineage &amp; Sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Preventive maintenance task list and interval schedule for critical equipment on Line 2, used to plan planned downtime windows. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Records document lineage, governance metadata, version history, and owner sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 12.1: PM compliance rate is reported alongside the monthly OEE review. Secondary control 12.2: Lubrication checks on the conveyor drive are performed weekly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Control Area</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Production Operations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Monitored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 12 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• PM compliance rate is reported alongside the monthly OEE review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Lubrication checks on the conveyor drive are performed weekly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 12 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Schedule - Line 2 - Section 2: Architecture &amp; Process Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Preventive maintenance task list and interval schedule for critical equipment on Line 2, used to plan planned downtime windows. Section 2 (Architecture &amp; Process Flow) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Maps end-to-end process stages, handoff gates, and system-of-record integrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 2.1: Full gearbox inspection is scheduled quarterly during planned downtime. Secondary control 2.2: Missed PM tasks are automatically rolled into the following week's schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Control Area</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Production Operations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Monitored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 2 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Full gearbox inspection is scheduled quarterly during planned downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Missed PM tasks are automatically rolled into the following week's schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 2 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Schedule - Line 2 - Section 3: Governance Standards &amp; Controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Preventive maintenance task list and interval schedule for critical equipment on Line 2, used to plan planned downtime windows. Section 3 (Governance Standards &amp; Controls) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Establishes mandatory compliance controls, approval thresholds, and audit evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 3.1: Missed PM tasks are automatically rolled into the following week's schedule. Secondary control 3.2: PM compliance rate is reported alongside the monthly OEE review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Control Area</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Production Operations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Monitored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 3 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Missed PM tasks are automatically rolled into the following week's schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• PM compliance rate is reported alongside the monthly OEE review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 3 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Schedule - Line 2 - Section 4: Operational KPIs &amp; Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Preventive maintenance task list and interval schedule for critical equipment on Line 2, used to plan planned downtime windows. Section 4 (Operational KPIs &amp; Benchmarks) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Tracks baseline performance, target SLAs, and quarterly benchmark progression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 4.1: PM compliance rate is reported alongside the monthly OEE review. Secondary control 4.2: Lubrication checks on the conveyor drive are performed weekly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Control Area</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Production Operations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Monitored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 4 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• PM compliance rate is reported alongside the monthly OEE review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Lubrication checks on the conveyor drive are performed weekly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 4 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Schedule - Line 2 - Section 5: Roles, Responsibilities &amp; RACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Preventive maintenance task list and interval schedule for critical equipment on Line 2, used to plan planned downtime windows. Section 5 (Roles, Responsibilities &amp; RACI) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Clarifies ownership across accountable executives, operational leads, and reviewers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 5.1: Lubrication checks on the conveyor drive are performed weekly. Secondary control 5.2: Full gearbox inspection is scheduled quarterly during planned downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Control Area</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Production Operations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Monitored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 5 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Lubrication checks on the conveyor drive are performed weekly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Full gearbox inspection is scheduled quarterly during planned downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 5 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Schedule - Line 2 - Section 6: Standard Operating Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Preventive maintenance task list and interval schedule for critical equipment on Line 2, used to plan planned downtime windows. Section 6 (Standard Operating Procedures) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Provides step-by-step execution checklists, intake criteria, and verification gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 6.1: Full gearbox inspection is scheduled quarterly during planned downtime. Secondary control 6.2: Missed PM tasks are automatically rolled into the following week's schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Control Area</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Production Operations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Monitored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 6 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Full gearbox inspection is scheduled quarterly during planned downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Missed PM tasks are automatically rolled into the following week's schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 6 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Schedule - Line 2 - Section 7: Risk Register &amp; Mitigations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Preventive maintenance task list and interval schedule for critical equipment on Line 2, used to plan planned downtime windows. Section 7 (Risk Register &amp; Mitigations) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Catalogs operational, compliance, and delivery risks alongside preventive mitigations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 7.1: Missed PM tasks are automatically rolled into the following week's schedule. Secondary control 7.2: PM compliance rate is reported alongside the monthly OEE review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Control Area</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Production Operations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Monitored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 7 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Missed PM tasks are automatically rolled into the following week's schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• PM compliance rate is reported alongside the monthly OEE review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 7 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Schedule - Line 2 - Section 8: Quality Assurance &amp; Audits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Preventive maintenance task list and interval schedule for critical equipment on Line 2, used to plan planned downtime windows. Section 8 (Quality Assurance &amp; Audits) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Specifies sampling frequencies, inspection tolerances, and nonconformance workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 8.1: PM compliance rate is reported alongside the monthly OEE review. Secondary control 8.2: Lubrication checks on the conveyor drive are performed weekly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Control Area</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Production Operations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Monitored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 8 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• PM compliance rate is reported alongside the monthly OEE review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Lubrication checks on the conveyor drive are performed weekly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 8 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Schedule - Line 2 - Section 9: Exception Handling &amp; Escalations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Preventive maintenance task list and interval schedule for critical equipment on Line 2, used to plan planned downtime windows. Section 9 (Exception Handling &amp; Escalations) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Outlines severity tiers, response SLAs, and cross-functional escalation paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 9.1: Lubrication checks on the conveyor drive are performed weekly. Secondary control 9.2: Full gearbox inspection is scheduled quarterly during planned downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Control Area</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Verification Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Production Operations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Sched Gate 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Monitored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grace Liu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stage 9 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Lubrication checks on the conveyor drive are performed weekly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Full gearbox inspection is scheduled quarterly during planned downtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 9 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>